--- a/log_reg_tests.xlsx
+++ b/log_reg_tests.xlsx
@@ -5,25 +5,26 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tewaka-my.sharepoint.com/personal/stw0454_arastudent_ac_nz/Documents/BCIT601 AI/Assign2/It1/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tewaka-my.sharepoint.com/personal/stw0454_arastudent_ac_nz/Documents/BCIT601 AI/Assign2/It2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="36" documentId="11_2CB4073B8AF8C29501264EE2F511E59ED31FAAC5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8370BC61-DA92-4F0C-87D8-2023394D6ABF}"/>
+  <xr:revisionPtr revIDLastSave="295" documentId="11_2CB4073B8AF8C29501264EE2F511E59ED31FAAC5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3ED71CA9-A9CA-4FF6-9A83-51154AD53994}"/>
   <bookViews>
-    <workbookView xWindow="-14505" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-27615" yWindow="2715" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="11" r:id="rId1"/>
-    <sheet name="rand_42" sheetId="1" r:id="rId2"/>
-    <sheet name="rand_1" sheetId="2" r:id="rId3"/>
-    <sheet name="rand_2" sheetId="3" r:id="rId4"/>
-    <sheet name="rand_3" sheetId="4" r:id="rId5"/>
-    <sheet name="rand_4" sheetId="5" r:id="rId6"/>
-    <sheet name="rand_5" sheetId="6" r:id="rId7"/>
-    <sheet name="rand_6" sheetId="7" r:id="rId8"/>
-    <sheet name="rand_7" sheetId="8" r:id="rId9"/>
-    <sheet name="rand_8" sheetId="9" r:id="rId10"/>
-    <sheet name="rand_9" sheetId="10" r:id="rId11"/>
+    <sheet name="workings" sheetId="12" r:id="rId1"/>
+    <sheet name="Summary" sheetId="11" r:id="rId2"/>
+    <sheet name="rand_42" sheetId="1" r:id="rId3"/>
+    <sheet name="rand_1" sheetId="2" r:id="rId4"/>
+    <sheet name="rand_2" sheetId="3" r:id="rId5"/>
+    <sheet name="rand_3" sheetId="4" r:id="rId6"/>
+    <sheet name="rand_4" sheetId="5" r:id="rId7"/>
+    <sheet name="rand_5" sheetId="6" r:id="rId8"/>
+    <sheet name="rand_6" sheetId="7" r:id="rId9"/>
+    <sheet name="rand_7" sheetId="8" r:id="rId10"/>
+    <sheet name="rand_8" sheetId="9" r:id="rId11"/>
+    <sheet name="rand_9" sheetId="10" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,8 +43,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1035" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1310" uniqueCount="160">
   <si>
     <t>Request_text</t>
   </si>
@@ -484,16 +507,61 @@
   </si>
   <si>
     <t>Test</t>
+  </si>
+  <si>
+    <t>rand_42</t>
+  </si>
+  <si>
+    <t>rand_1</t>
+  </si>
+  <si>
+    <t>rand_2</t>
+  </si>
+  <si>
+    <t>rand_3</t>
+  </si>
+  <si>
+    <t>rand_4</t>
+  </si>
+  <si>
+    <t>rand_5</t>
+  </si>
+  <si>
+    <t>rand_6</t>
+  </si>
+  <si>
+    <t>rand_7</t>
+  </si>
+  <si>
+    <t>rand_8</t>
+  </si>
+  <si>
+    <t>rand_9</t>
+  </si>
+  <si>
+    <t>Test #</t>
+  </si>
+  <si>
+    <t>Prediction</t>
+  </si>
+  <si>
+    <t>Actual</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -519,13 +587,38 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -536,6 +629,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -824,138 +921,1074 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE26576B-4601-404F-A174-823BF0301A82}">
-  <dimension ref="A1:B15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D17390B7-A0CE-4205-8090-B9CAD544B5CF}">
+  <dimension ref="A1:M120"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="4" max="4" width="8.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="19" width="6.77734375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+      <c r="B1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>146</v>
+        <v>18</v>
       </c>
       <c r="B2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" t="s">
+        <v>159</v>
+      </c>
+      <c r="I3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J3">
+        <f>COUNTIFS($B:$B,J$2,$A:$A,$I3)</f>
+        <v>8</v>
+      </c>
+      <c r="K3">
+        <f>COUNTIFS($B:$B,K$2,$A:$A,$I3)</f>
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3">
+      <c r="L3">
+        <f>COUNTIFS($B:$B,L$2,$A:$A,$I3)</f>
+        <v>12</v>
+      </c>
+      <c r="M3">
+        <f>COUNTIFS($B:$B,M$2,$A:$A,$I3)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J4">
+        <f>COUNTIFS($B:$B,J$2,$A:$A,$I4)</f>
+        <v>2</v>
+      </c>
+      <c r="K4">
+        <f>COUNTIFS($B:$B,K$2,$A:$A,$I4)</f>
+        <v>20</v>
+      </c>
+      <c r="L4">
+        <f>COUNTIFS($B:$B,L$2,$A:$A,$I4)</f>
+        <v>8</v>
+      </c>
+      <c r="M4">
+        <f>COUNTIFS($B:$B,M$2,$A:$A,$I4)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I5" t="s">
+        <v>18</v>
+      </c>
+      <c r="J5">
+        <f>COUNTIFS($B:$B,J$2,$A:$A,$I5)</f>
+        <v>9</v>
+      </c>
+      <c r="K5">
+        <f>COUNTIFS($B:$B,K$2,$A:$A,$I5)</f>
+        <v>2</v>
+      </c>
+      <c r="L5">
+        <f>COUNTIFS($B:$B,L$2,$A:$A,$I5)</f>
+        <v>18</v>
+      </c>
+      <c r="M5">
+        <f>COUNTIFS($B:$B,M$2,$A:$A,$I5)</f>
         <v>1</v>
       </c>
-      <c r="B3">
-        <f>rand_42!F2</f>
-        <v>0.66666666666666663</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>2</v>
-      </c>
-      <c r="B4">
-        <f>rand_1!$F$2</f>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>3</v>
-      </c>
-      <c r="B5">
-        <f>rand_2!$F$2</f>
-        <v>0.66666666666666663</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6">
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>20</v>
+      </c>
+      <c r="I6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J6">
+        <f>COUNTIFS($B:$B,J$2,$A:$A,$I6)</f>
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <f>COUNTIFS($B:$B,K$2,$A:$A,$I6)</f>
         <v>4</v>
       </c>
-      <c r="B6">
-        <f>rand_3!$F$2</f>
-        <v>0.58333333333333337</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>5</v>
-      </c>
-      <c r="B7">
-        <f>rand_4!$F$2</f>
-        <v>0.58333333333333337</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>6</v>
-      </c>
-      <c r="B8">
-        <f>rand_5!$F$2</f>
-        <v>0.58333333333333337</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>7</v>
-      </c>
-      <c r="B9">
-        <f>rand_6!$F$2</f>
-        <v>0.66666666666666663</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>8</v>
-      </c>
-      <c r="B10">
-        <f>rand_7!$F$2</f>
-        <v>0.66666666666666663</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>9</v>
-      </c>
-      <c r="B11">
-        <f>rand_8!$F$2</f>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12">
-        <v>10</v>
-      </c>
-      <c r="B12">
-        <f>rand_9!$F$2</f>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="L6">
+        <f>COUNTIFS($B:$B,L$2,$A:$A,$I6)</f>
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <f>COUNTIFS($B:$B,M$2,$A:$A,$I6)</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>143</v>
-      </c>
-      <c r="B13">
-        <f>MIN(B3:B12)</f>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+      <c r="B13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>144</v>
-      </c>
-      <c r="B14">
-        <f>MAX(B3:B12)</f>
-        <v>0.66666666666666663</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+      <c r="B14" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>145</v>
-      </c>
-      <c r="B15">
-        <f>AVERAGE(B3:B12)</f>
-        <v>0.59166666666666667</v>
+        <v>19</v>
+      </c>
+      <c r="B15" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>20</v>
+      </c>
+      <c r="B19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>18</v>
+      </c>
+      <c r="B22" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>18</v>
+      </c>
+      <c r="B23" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>17</v>
+      </c>
+      <c r="B24" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>18</v>
+      </c>
+      <c r="B25" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>20</v>
+      </c>
+      <c r="B26" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>19</v>
+      </c>
+      <c r="B27" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>19</v>
+      </c>
+      <c r="B28" t="s">
+        <v>18</v>
+      </c>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>20</v>
+      </c>
+      <c r="B29" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>19</v>
+      </c>
+      <c r="B30" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>17</v>
+      </c>
+      <c r="B31" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>17</v>
+      </c>
+      <c r="B32" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>18</v>
+      </c>
+      <c r="B33" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>18</v>
+      </c>
+      <c r="B34" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>17</v>
+      </c>
+      <c r="B35" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>20</v>
+      </c>
+      <c r="B36" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>20</v>
+      </c>
+      <c r="B37" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>18</v>
+      </c>
+      <c r="B38" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>17</v>
+      </c>
+      <c r="B39" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>19</v>
+      </c>
+      <c r="B40" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>17</v>
+      </c>
+      <c r="B41" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>18</v>
+      </c>
+      <c r="B42" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>20</v>
+      </c>
+      <c r="B43" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>18</v>
+      </c>
+      <c r="B44" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>17</v>
+      </c>
+      <c r="B45" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>19</v>
+      </c>
+      <c r="B46" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>20</v>
+      </c>
+      <c r="B47" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>19</v>
+      </c>
+      <c r="B48" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>18</v>
+      </c>
+      <c r="B49" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>18</v>
+      </c>
+      <c r="B50" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>20</v>
+      </c>
+      <c r="B51" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>17</v>
+      </c>
+      <c r="B52" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>19</v>
+      </c>
+      <c r="B53" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>19</v>
+      </c>
+      <c r="B54" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>18</v>
+      </c>
+      <c r="B55" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>17</v>
+      </c>
+      <c r="B56" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>17</v>
+      </c>
+      <c r="B57" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>20</v>
+      </c>
+      <c r="B58" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>19</v>
+      </c>
+      <c r="B59" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>20</v>
+      </c>
+      <c r="B60" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>18</v>
+      </c>
+      <c r="B61" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>20</v>
+      </c>
+      <c r="B62" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>19</v>
+      </c>
+      <c r="B63" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>20</v>
+      </c>
+      <c r="B64" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>17</v>
+      </c>
+      <c r="B65" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>18</v>
+      </c>
+      <c r="B66" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>17</v>
+      </c>
+      <c r="B67" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>18</v>
+      </c>
+      <c r="B68" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>19</v>
+      </c>
+      <c r="B69" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>20</v>
+      </c>
+      <c r="B70" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>17</v>
+      </c>
+      <c r="B71" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>19</v>
+      </c>
+      <c r="B72" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>20</v>
+      </c>
+      <c r="B73" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>17</v>
+      </c>
+      <c r="B74" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>19</v>
+      </c>
+      <c r="B75" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>20</v>
+      </c>
+      <c r="B76" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>20</v>
+      </c>
+      <c r="B77" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>18</v>
+      </c>
+      <c r="B78" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>17</v>
+      </c>
+      <c r="B79" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>18</v>
+      </c>
+      <c r="B80" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>19</v>
+      </c>
+      <c r="B81" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>18</v>
+      </c>
+      <c r="B82" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>17</v>
+      </c>
+      <c r="B83" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>19</v>
+      </c>
+      <c r="B84" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>19</v>
+      </c>
+      <c r="B85" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>19</v>
+      </c>
+      <c r="B86" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>19</v>
+      </c>
+      <c r="B87" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>20</v>
+      </c>
+      <c r="B88" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>18</v>
+      </c>
+      <c r="B89" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>20</v>
+      </c>
+      <c r="B90" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>18</v>
+      </c>
+      <c r="B91" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>20</v>
+      </c>
+      <c r="B92" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>17</v>
+      </c>
+      <c r="B93" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>17</v>
+      </c>
+      <c r="B94" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>18</v>
+      </c>
+      <c r="B95" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>17</v>
+      </c>
+      <c r="B96" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>18</v>
+      </c>
+      <c r="B97" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>17</v>
+      </c>
+      <c r="B98" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>17</v>
+      </c>
+      <c r="B99" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>17</v>
+      </c>
+      <c r="B100" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>20</v>
+      </c>
+      <c r="B101" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>18</v>
+      </c>
+      <c r="B102" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>19</v>
+      </c>
+      <c r="B103" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>18</v>
+      </c>
+      <c r="B104" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>19</v>
+      </c>
+      <c r="B105" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>20</v>
+      </c>
+      <c r="B106" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>20</v>
+      </c>
+      <c r="B107" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>19</v>
+      </c>
+      <c r="B108" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>20</v>
+      </c>
+      <c r="B109" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>20</v>
+      </c>
+      <c r="B110" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>17</v>
+      </c>
+      <c r="B111" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>18</v>
+      </c>
+      <c r="B112" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>18</v>
+      </c>
+      <c r="B113" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>19</v>
+      </c>
+      <c r="B114" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>20</v>
+      </c>
+      <c r="B115" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>19</v>
+      </c>
+      <c r="B116" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>18</v>
+      </c>
+      <c r="B117" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>19</v>
+      </c>
+      <c r="B118" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>17</v>
+      </c>
+      <c r="B119" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>17</v>
+      </c>
+      <c r="B120" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -964,6 +1997,616 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="A1:F60"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>120</v>
+      </c>
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>126</v>
+      </c>
+      <c r="C7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>135</v>
+      </c>
+      <c r="C8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>99</v>
+      </c>
+      <c r="C9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" t="s">
+        <v>17</v>
+      </c>
+      <c r="E10" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>136</v>
+      </c>
+      <c r="C11" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E11" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>137</v>
+      </c>
+      <c r="C12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C13" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" t="s">
+        <v>17</v>
+      </c>
+      <c r="E13" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="E14" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="E15" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="E16" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="E17" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>16</v>
+      </c>
+      <c r="E18" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>17</v>
+      </c>
+      <c r="E19" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>18</v>
+      </c>
+      <c r="E20" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>19</v>
+      </c>
+      <c r="E21" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>20</v>
+      </c>
+      <c r="E22" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>21</v>
+      </c>
+      <c r="E23" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>22</v>
+      </c>
+      <c r="E24" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>23</v>
+      </c>
+      <c r="E25" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>24</v>
+      </c>
+      <c r="E26" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>25</v>
+      </c>
+      <c r="E27" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>26</v>
+      </c>
+      <c r="E28" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>27</v>
+      </c>
+      <c r="E29" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>28</v>
+      </c>
+      <c r="E30" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>29</v>
+      </c>
+      <c r="E31" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <v>30</v>
+      </c>
+      <c r="E32" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33">
+        <v>31</v>
+      </c>
+      <c r="E33" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34">
+        <v>32</v>
+      </c>
+      <c r="E34" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35">
+        <v>33</v>
+      </c>
+      <c r="E35" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36">
+        <v>34</v>
+      </c>
+      <c r="E36" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37">
+        <v>35</v>
+      </c>
+      <c r="E37" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A38">
+        <v>36</v>
+      </c>
+      <c r="E38" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A39">
+        <v>37</v>
+      </c>
+      <c r="E39" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A40">
+        <v>38</v>
+      </c>
+      <c r="E40" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A41">
+        <v>39</v>
+      </c>
+      <c r="E41" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A42">
+        <v>40</v>
+      </c>
+      <c r="E42" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A43">
+        <v>41</v>
+      </c>
+      <c r="E43" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A44">
+        <v>42</v>
+      </c>
+      <c r="E44" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A45">
+        <v>43</v>
+      </c>
+      <c r="E45" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A46">
+        <v>44</v>
+      </c>
+      <c r="E46" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A47">
+        <v>45</v>
+      </c>
+      <c r="E47" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A48">
+        <v>46</v>
+      </c>
+      <c r="E48" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A49">
+        <v>47</v>
+      </c>
+      <c r="E49" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A50">
+        <v>48</v>
+      </c>
+      <c r="E50" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A51">
+        <v>49</v>
+      </c>
+      <c r="E51" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A52">
+        <v>50</v>
+      </c>
+      <c r="E52" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A53">
+        <v>51</v>
+      </c>
+      <c r="E53" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A54">
+        <v>52</v>
+      </c>
+      <c r="E54" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A55">
+        <v>53</v>
+      </c>
+      <c r="E55" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A56">
+        <v>54</v>
+      </c>
+      <c r="E56" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A57">
+        <v>55</v>
+      </c>
+      <c r="E57" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A58">
+        <v>56</v>
+      </c>
+      <c r="E58" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A59">
+        <v>57</v>
+      </c>
+      <c r="E59" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A60">
+        <v>58</v>
+      </c>
+      <c r="E60" t="s">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:F61"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1581,7 +3224,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:F65"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2235,6 +3878,1565 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE26576B-4601-404F-A174-823BF0301A82}">
+  <dimension ref="A1:W19"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="4" max="5" width="7.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="19" width="6.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C1" t="s">
+        <v>157</v>
+      </c>
+      <c r="D1" t="s">
+        <v>147</v>
+      </c>
+      <c r="E1" t="s">
+        <v>147</v>
+      </c>
+      <c r="F1" t="s">
+        <v>148</v>
+      </c>
+      <c r="G1" t="s">
+        <v>148</v>
+      </c>
+      <c r="H1" t="s">
+        <v>149</v>
+      </c>
+      <c r="I1" t="s">
+        <v>149</v>
+      </c>
+      <c r="J1" t="s">
+        <v>150</v>
+      </c>
+      <c r="K1" t="s">
+        <v>150</v>
+      </c>
+      <c r="L1" t="s">
+        <v>151</v>
+      </c>
+      <c r="M1" t="s">
+        <v>151</v>
+      </c>
+      <c r="N1" t="s">
+        <v>152</v>
+      </c>
+      <c r="O1" t="s">
+        <v>152</v>
+      </c>
+      <c r="P1" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>153</v>
+      </c>
+      <c r="R1" t="s">
+        <v>154</v>
+      </c>
+      <c r="S1" t="s">
+        <v>154</v>
+      </c>
+      <c r="T1" t="s">
+        <v>155</v>
+      </c>
+      <c r="U1" t="s">
+        <v>155</v>
+      </c>
+      <c r="V1" t="s">
+        <v>156</v>
+      </c>
+      <c r="W1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="str" cm="1">
+        <f t="array" aca="1" ref="D2" ca="1">INDIRECT("'"&amp;D$1&amp;"'!" &amp; ADDRESS($C2+1,3))</f>
+        <v>waste</v>
+      </c>
+      <c r="E2" t="str" cm="1">
+        <f t="array" aca="1" ref="E2" ca="1">INDIRECT("'"&amp;E$1&amp;"'!" &amp; ADDRESS($C2+1,4))</f>
+        <v>waste</v>
+      </c>
+      <c r="F2" t="str" cm="1">
+        <f t="array" aca="1" ref="F2" ca="1">INDIRECT("'"&amp;F$1&amp;"'!" &amp; ADDRESS($C2+1,3))</f>
+        <v>waste</v>
+      </c>
+      <c r="G2" t="str" cm="1">
+        <f t="array" aca="1" ref="G2" ca="1">INDIRECT("'"&amp;G$1&amp;"'!" &amp; ADDRESS($C2+1,4))</f>
+        <v>waste</v>
+      </c>
+      <c r="H2" t="str" cm="1">
+        <f t="array" aca="1" ref="H2" ca="1">INDIRECT("'"&amp;H$1&amp;"'!" &amp; ADDRESS($C2+1,3))</f>
+        <v>safety</v>
+      </c>
+      <c r="I2" t="str" cm="1">
+        <f t="array" aca="1" ref="I2" ca="1">INDIRECT("'"&amp;I$1&amp;"'!" &amp; ADDRESS($C2+1,4))</f>
+        <v>safety</v>
+      </c>
+      <c r="J2" t="str" cm="1">
+        <f t="array" aca="1" ref="J2" ca="1">INDIRECT("'"&amp;J$1&amp;"'!" &amp; ADDRESS($C2+1,3))</f>
+        <v>water</v>
+      </c>
+      <c r="K2" t="str" cm="1">
+        <f t="array" aca="1" ref="K2" ca="1">INDIRECT("'"&amp;K$1&amp;"'!" &amp; ADDRESS($C2+1,4))</f>
+        <v>water</v>
+      </c>
+      <c r="L2" t="str" cm="1">
+        <f t="array" aca="1" ref="L2" ca="1">INDIRECT("'"&amp;L$1&amp;"'!" &amp; ADDRESS($C2+1,3))</f>
+        <v>safety</v>
+      </c>
+      <c r="M2" t="str" cm="1">
+        <f t="array" aca="1" ref="M2" ca="1">INDIRECT("'"&amp;M$1&amp;"'!" &amp; ADDRESS($C2+1,4))</f>
+        <v>safety</v>
+      </c>
+      <c r="N2" t="str" cm="1">
+        <f t="array" aca="1" ref="N2" ca="1">INDIRECT("'"&amp;N$1&amp;"'!" &amp; ADDRESS($C2+1,3))</f>
+        <v>safety</v>
+      </c>
+      <c r="O2" t="str" cm="1">
+        <f t="array" aca="1" ref="O2" ca="1">INDIRECT("'"&amp;O$1&amp;"'!" &amp; ADDRESS($C2+1,4))</f>
+        <v>safety</v>
+      </c>
+      <c r="P2" t="str" cm="1">
+        <f t="array" aca="1" ref="P2" ca="1">INDIRECT("'"&amp;P$1&amp;"'!" &amp; ADDRESS($C2+1,3))</f>
+        <v>water</v>
+      </c>
+      <c r="Q2" t="str" cm="1">
+        <f t="array" aca="1" ref="Q2" ca="1">INDIRECT("'"&amp;Q$1&amp;"'!" &amp; ADDRESS($C2+1,4))</f>
+        <v>waste</v>
+      </c>
+      <c r="R2" t="str" cm="1">
+        <f t="array" aca="1" ref="R2" ca="1">INDIRECT("'"&amp;R$1&amp;"'!" &amp; ADDRESS($C2+1,3))</f>
+        <v>road</v>
+      </c>
+      <c r="S2" t="str" cm="1">
+        <f t="array" aca="1" ref="S2" ca="1">INDIRECT("'"&amp;S$1&amp;"'!" &amp; ADDRESS($C2+1,4))</f>
+        <v>water</v>
+      </c>
+      <c r="T2" t="str" cm="1">
+        <f t="array" aca="1" ref="T2" ca="1">INDIRECT("'"&amp;T$1&amp;"'!" &amp; ADDRESS($C2+1,3))</f>
+        <v>safety</v>
+      </c>
+      <c r="U2" t="str" cm="1">
+        <f t="array" aca="1" ref="U2" ca="1">INDIRECT("'"&amp;U$1&amp;"'!" &amp; ADDRESS($C2+1,4))</f>
+        <v>road</v>
+      </c>
+      <c r="V2" t="str" cm="1">
+        <f t="array" aca="1" ref="V2" ca="1">INDIRECT("'"&amp;V$1&amp;"'!" &amp; ADDRESS($C2+1,3))</f>
+        <v>water</v>
+      </c>
+      <c r="W2" t="str" cm="1">
+        <f t="array" aca="1" ref="W2" ca="1">INDIRECT("'"&amp;W$1&amp;"'!" &amp; ADDRESS($C2+1,4))</f>
+        <v>water</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <f>rand_42!F2</f>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3" t="str" cm="1">
+        <f t="array" aca="1" ref="D3" ca="1">INDIRECT("'"&amp;D$1&amp;"'!" &amp; ADDRESS($C3+1,3))</f>
+        <v>safety</v>
+      </c>
+      <c r="E3" t="str" cm="1">
+        <f t="array" aca="1" ref="E3" ca="1">INDIRECT("'"&amp;E$1&amp;"'!" &amp; ADDRESS($C3+1,4))</f>
+        <v>safety</v>
+      </c>
+      <c r="F3" t="str" cm="1">
+        <f t="array" aca="1" ref="F3" ca="1">INDIRECT("'"&amp;F$1&amp;"'!" &amp; ADDRESS($C3+1,3))</f>
+        <v>road</v>
+      </c>
+      <c r="G3" t="str" cm="1">
+        <f t="array" aca="1" ref="G3" ca="1">INDIRECT("'"&amp;G$1&amp;"'!" &amp; ADDRESS($C3+1,4))</f>
+        <v>safety</v>
+      </c>
+      <c r="H3" t="str" cm="1">
+        <f t="array" aca="1" ref="H3" ca="1">INDIRECT("'"&amp;H$1&amp;"'!" &amp; ADDRESS($C3+1,3))</f>
+        <v>water</v>
+      </c>
+      <c r="I3" t="str" cm="1">
+        <f t="array" aca="1" ref="I3" ca="1">INDIRECT("'"&amp;I$1&amp;"'!" &amp; ADDRESS($C3+1,4))</f>
+        <v>water</v>
+      </c>
+      <c r="J3" t="str" cm="1">
+        <f t="array" aca="1" ref="J3" ca="1">INDIRECT("'"&amp;J$1&amp;"'!" &amp; ADDRESS($C3+1,3))</f>
+        <v>safety</v>
+      </c>
+      <c r="K3" t="str" cm="1">
+        <f t="array" aca="1" ref="K3" ca="1">INDIRECT("'"&amp;K$1&amp;"'!" &amp; ADDRESS($C3+1,4))</f>
+        <v>road</v>
+      </c>
+      <c r="L3" t="str" cm="1">
+        <f t="array" aca="1" ref="L3" ca="1">INDIRECT("'"&amp;L$1&amp;"'!" &amp; ADDRESS($C3+1,3))</f>
+        <v>safety</v>
+      </c>
+      <c r="M3" t="str" cm="1">
+        <f t="array" aca="1" ref="M3" ca="1">INDIRECT("'"&amp;M$1&amp;"'!" &amp; ADDRESS($C3+1,4))</f>
+        <v>road</v>
+      </c>
+      <c r="N3" t="str" cm="1">
+        <f t="array" aca="1" ref="N3" ca="1">INDIRECT("'"&amp;N$1&amp;"'!" &amp; ADDRESS($C3+1,3))</f>
+        <v>water</v>
+      </c>
+      <c r="O3" t="str" cm="1">
+        <f t="array" aca="1" ref="O3" ca="1">INDIRECT("'"&amp;O$1&amp;"'!" &amp; ADDRESS($C3+1,4))</f>
+        <v>water</v>
+      </c>
+      <c r="P3" t="str" cm="1">
+        <f t="array" aca="1" ref="P3" ca="1">INDIRECT("'"&amp;P$1&amp;"'!" &amp; ADDRESS($C3+1,3))</f>
+        <v>waste</v>
+      </c>
+      <c r="Q3" t="str" cm="1">
+        <f t="array" aca="1" ref="Q3" ca="1">INDIRECT("'"&amp;Q$1&amp;"'!" &amp; ADDRESS($C3+1,4))</f>
+        <v>waste</v>
+      </c>
+      <c r="R3" t="str" cm="1">
+        <f t="array" aca="1" ref="R3" ca="1">INDIRECT("'"&amp;R$1&amp;"'!" &amp; ADDRESS($C3+1,3))</f>
+        <v>road</v>
+      </c>
+      <c r="S3" t="str" cm="1">
+        <f t="array" aca="1" ref="S3" ca="1">INDIRECT("'"&amp;S$1&amp;"'!" &amp; ADDRESS($C3+1,4))</f>
+        <v>safety</v>
+      </c>
+      <c r="T3" t="str" cm="1">
+        <f t="array" aca="1" ref="T3" ca="1">INDIRECT("'"&amp;T$1&amp;"'!" &amp; ADDRESS($C3+1,3))</f>
+        <v>waste</v>
+      </c>
+      <c r="U3" t="str" cm="1">
+        <f t="array" aca="1" ref="U3" ca="1">INDIRECT("'"&amp;U$1&amp;"'!" &amp; ADDRESS($C3+1,4))</f>
+        <v>waste</v>
+      </c>
+      <c r="V3" t="str" cm="1">
+        <f t="array" aca="1" ref="V3" ca="1">INDIRECT("'"&amp;V$1&amp;"'!" &amp; ADDRESS($C3+1,3))</f>
+        <v>water</v>
+      </c>
+      <c r="W3" t="str" cm="1">
+        <f t="array" aca="1" ref="W3" ca="1">INDIRECT("'"&amp;W$1&amp;"'!" &amp; ADDRESS($C3+1,4))</f>
+        <v>water</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <f>rand_1!$F$2</f>
+        <v>0.5</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+      <c r="D4" t="str" cm="1">
+        <f t="array" aca="1" ref="D4" ca="1">INDIRECT("'"&amp;D$1&amp;"'!" &amp; ADDRESS($C4+1,3))</f>
+        <v>safety</v>
+      </c>
+      <c r="E4" t="str" cm="1">
+        <f t="array" aca="1" ref="E4" ca="1">INDIRECT("'"&amp;E$1&amp;"'!" &amp; ADDRESS($C4+1,4))</f>
+        <v>safety</v>
+      </c>
+      <c r="F4" t="str" cm="1">
+        <f t="array" aca="1" ref="F4" ca="1">INDIRECT("'"&amp;F$1&amp;"'!" &amp; ADDRESS($C4+1,3))</f>
+        <v>road</v>
+      </c>
+      <c r="G4" t="str" cm="1">
+        <f t="array" aca="1" ref="G4" ca="1">INDIRECT("'"&amp;G$1&amp;"'!" &amp; ADDRESS($C4+1,4))</f>
+        <v>safety</v>
+      </c>
+      <c r="H4" t="str" cm="1">
+        <f t="array" aca="1" ref="H4" ca="1">INDIRECT("'"&amp;H$1&amp;"'!" &amp; ADDRESS($C4+1,3))</f>
+        <v>road</v>
+      </c>
+      <c r="I4" t="str" cm="1">
+        <f t="array" aca="1" ref="I4" ca="1">INDIRECT("'"&amp;I$1&amp;"'!" &amp; ADDRESS($C4+1,4))</f>
+        <v>road</v>
+      </c>
+      <c r="J4" t="str" cm="1">
+        <f t="array" aca="1" ref="J4" ca="1">INDIRECT("'"&amp;J$1&amp;"'!" &amp; ADDRESS($C4+1,3))</f>
+        <v>waste</v>
+      </c>
+      <c r="K4" t="str" cm="1">
+        <f t="array" aca="1" ref="K4" ca="1">INDIRECT("'"&amp;K$1&amp;"'!" &amp; ADDRESS($C4+1,4))</f>
+        <v>safety</v>
+      </c>
+      <c r="L4" t="str" cm="1">
+        <f t="array" aca="1" ref="L4" ca="1">INDIRECT("'"&amp;L$1&amp;"'!" &amp; ADDRESS($C4+1,3))</f>
+        <v>water</v>
+      </c>
+      <c r="M4" t="str" cm="1">
+        <f t="array" aca="1" ref="M4" ca="1">INDIRECT("'"&amp;M$1&amp;"'!" &amp; ADDRESS($C4+1,4))</f>
+        <v>water</v>
+      </c>
+      <c r="N4" t="str" cm="1">
+        <f t="array" aca="1" ref="N4" ca="1">INDIRECT("'"&amp;N$1&amp;"'!" &amp; ADDRESS($C4+1,3))</f>
+        <v>road</v>
+      </c>
+      <c r="O4" t="str" cm="1">
+        <f t="array" aca="1" ref="O4" ca="1">INDIRECT("'"&amp;O$1&amp;"'!" &amp; ADDRESS($C4+1,4))</f>
+        <v>safety</v>
+      </c>
+      <c r="P4" t="str" cm="1">
+        <f t="array" aca="1" ref="P4" ca="1">INDIRECT("'"&amp;P$1&amp;"'!" &amp; ADDRESS($C4+1,3))</f>
+        <v>road</v>
+      </c>
+      <c r="Q4" t="str" cm="1">
+        <f t="array" aca="1" ref="Q4" ca="1">INDIRECT("'"&amp;Q$1&amp;"'!" &amp; ADDRESS($C4+1,4))</f>
+        <v>road</v>
+      </c>
+      <c r="R4" t="str" cm="1">
+        <f t="array" aca="1" ref="R4" ca="1">INDIRECT("'"&amp;R$1&amp;"'!" &amp; ADDRESS($C4+1,3))</f>
+        <v>road</v>
+      </c>
+      <c r="S4" t="str" cm="1">
+        <f t="array" aca="1" ref="S4" ca="1">INDIRECT("'"&amp;S$1&amp;"'!" &amp; ADDRESS($C4+1,4))</f>
+        <v>safety</v>
+      </c>
+      <c r="T4" t="str" cm="1">
+        <f t="array" aca="1" ref="T4" ca="1">INDIRECT("'"&amp;T$1&amp;"'!" &amp; ADDRESS($C4+1,3))</f>
+        <v>waste</v>
+      </c>
+      <c r="U4" t="str" cm="1">
+        <f t="array" aca="1" ref="U4" ca="1">INDIRECT("'"&amp;U$1&amp;"'!" &amp; ADDRESS($C4+1,4))</f>
+        <v>safety</v>
+      </c>
+      <c r="V4" t="str" cm="1">
+        <f t="array" aca="1" ref="V4" ca="1">INDIRECT("'"&amp;V$1&amp;"'!" &amp; ADDRESS($C4+1,3))</f>
+        <v>waste</v>
+      </c>
+      <c r="W4" t="str" cm="1">
+        <f t="array" aca="1" ref="W4" ca="1">INDIRECT("'"&amp;W$1&amp;"'!" &amp; ADDRESS($C4+1,4))</f>
+        <v>waste</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <f>rand_2!$F$2</f>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5" t="str" cm="1">
+        <f t="array" aca="1" ref="D5" ca="1">INDIRECT("'"&amp;D$1&amp;"'!" &amp; ADDRESS($C5+1,3))</f>
+        <v>road</v>
+      </c>
+      <c r="E5" t="str" cm="1">
+        <f t="array" aca="1" ref="E5" ca="1">INDIRECT("'"&amp;E$1&amp;"'!" &amp; ADDRESS($C5+1,4))</f>
+        <v>safety</v>
+      </c>
+      <c r="F5" t="str" cm="1">
+        <f t="array" aca="1" ref="F5" ca="1">INDIRECT("'"&amp;F$1&amp;"'!" &amp; ADDRESS($C5+1,3))</f>
+        <v>waste</v>
+      </c>
+      <c r="G5" t="str" cm="1">
+        <f t="array" aca="1" ref="G5" ca="1">INDIRECT("'"&amp;G$1&amp;"'!" &amp; ADDRESS($C5+1,4))</f>
+        <v>waste</v>
+      </c>
+      <c r="H5" t="str" cm="1">
+        <f t="array" aca="1" ref="H5" ca="1">INDIRECT("'"&amp;H$1&amp;"'!" &amp; ADDRESS($C5+1,3))</f>
+        <v>road</v>
+      </c>
+      <c r="I5" t="str" cm="1">
+        <f t="array" aca="1" ref="I5" ca="1">INDIRECT("'"&amp;I$1&amp;"'!" &amp; ADDRESS($C5+1,4))</f>
+        <v>safety</v>
+      </c>
+      <c r="J5" t="str" cm="1">
+        <f t="array" aca="1" ref="J5" ca="1">INDIRECT("'"&amp;J$1&amp;"'!" &amp; ADDRESS($C5+1,3))</f>
+        <v>road</v>
+      </c>
+      <c r="K5" t="str" cm="1">
+        <f t="array" aca="1" ref="K5" ca="1">INDIRECT("'"&amp;K$1&amp;"'!" &amp; ADDRESS($C5+1,4))</f>
+        <v>water</v>
+      </c>
+      <c r="L5" t="str" cm="1">
+        <f t="array" aca="1" ref="L5" ca="1">INDIRECT("'"&amp;L$1&amp;"'!" &amp; ADDRESS($C5+1,3))</f>
+        <v>waste</v>
+      </c>
+      <c r="M5" t="str" cm="1">
+        <f t="array" aca="1" ref="M5" ca="1">INDIRECT("'"&amp;M$1&amp;"'!" &amp; ADDRESS($C5+1,4))</f>
+        <v>waste</v>
+      </c>
+      <c r="N5" t="str" cm="1">
+        <f t="array" aca="1" ref="N5" ca="1">INDIRECT("'"&amp;N$1&amp;"'!" &amp; ADDRESS($C5+1,3))</f>
+        <v>water</v>
+      </c>
+      <c r="O5" t="str" cm="1">
+        <f t="array" aca="1" ref="O5" ca="1">INDIRECT("'"&amp;O$1&amp;"'!" &amp; ADDRESS($C5+1,4))</f>
+        <v>waste</v>
+      </c>
+      <c r="P5" t="str" cm="1">
+        <f t="array" aca="1" ref="P5" ca="1">INDIRECT("'"&amp;P$1&amp;"'!" &amp; ADDRESS($C5+1,3))</f>
+        <v>water</v>
+      </c>
+      <c r="Q5" t="str" cm="1">
+        <f t="array" aca="1" ref="Q5" ca="1">INDIRECT("'"&amp;Q$1&amp;"'!" &amp; ADDRESS($C5+1,4))</f>
+        <v>water</v>
+      </c>
+      <c r="R5" t="str" cm="1">
+        <f t="array" aca="1" ref="R5" ca="1">INDIRECT("'"&amp;R$1&amp;"'!" &amp; ADDRESS($C5+1,3))</f>
+        <v>water</v>
+      </c>
+      <c r="S5" t="str" cm="1">
+        <f t="array" aca="1" ref="S5" ca="1">INDIRECT("'"&amp;S$1&amp;"'!" &amp; ADDRESS($C5+1,4))</f>
+        <v>water</v>
+      </c>
+      <c r="T5" t="str" cm="1">
+        <f t="array" aca="1" ref="T5" ca="1">INDIRECT("'"&amp;T$1&amp;"'!" &amp; ADDRESS($C5+1,3))</f>
+        <v>waste</v>
+      </c>
+      <c r="U5" t="str" cm="1">
+        <f t="array" aca="1" ref="U5" ca="1">INDIRECT("'"&amp;U$1&amp;"'!" &amp; ADDRESS($C5+1,4))</f>
+        <v>safety</v>
+      </c>
+      <c r="V5" t="str" cm="1">
+        <f t="array" aca="1" ref="V5" ca="1">INDIRECT("'"&amp;V$1&amp;"'!" &amp; ADDRESS($C5+1,3))</f>
+        <v>safety</v>
+      </c>
+      <c r="W5" t="str" cm="1">
+        <f t="array" aca="1" ref="W5" ca="1">INDIRECT("'"&amp;W$1&amp;"'!" &amp; ADDRESS($C5+1,4))</f>
+        <v>road</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <f>rand_3!$F$2</f>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
+      <c r="D6" t="str" cm="1">
+        <f t="array" aca="1" ref="D6" ca="1">INDIRECT("'"&amp;D$1&amp;"'!" &amp; ADDRESS($C6+1,3))</f>
+        <v>safety</v>
+      </c>
+      <c r="E6" t="str" cm="1">
+        <f t="array" aca="1" ref="E6" ca="1">INDIRECT("'"&amp;E$1&amp;"'!" &amp; ADDRESS($C6+1,4))</f>
+        <v>safety</v>
+      </c>
+      <c r="F6" t="str" cm="1">
+        <f t="array" aca="1" ref="F6" ca="1">INDIRECT("'"&amp;F$1&amp;"'!" &amp; ADDRESS($C6+1,3))</f>
+        <v>water</v>
+      </c>
+      <c r="G6" t="str" cm="1">
+        <f t="array" aca="1" ref="G6" ca="1">INDIRECT("'"&amp;G$1&amp;"'!" &amp; ADDRESS($C6+1,4))</f>
+        <v>waste</v>
+      </c>
+      <c r="H6" t="str" cm="1">
+        <f t="array" aca="1" ref="H6" ca="1">INDIRECT("'"&amp;H$1&amp;"'!" &amp; ADDRESS($C6+1,3))</f>
+        <v>water</v>
+      </c>
+      <c r="I6" t="str" cm="1">
+        <f t="array" aca="1" ref="I6" ca="1">INDIRECT("'"&amp;I$1&amp;"'!" &amp; ADDRESS($C6+1,4))</f>
+        <v>water</v>
+      </c>
+      <c r="J6" t="str" cm="1">
+        <f t="array" aca="1" ref="J6" ca="1">INDIRECT("'"&amp;J$1&amp;"'!" &amp; ADDRESS($C6+1,3))</f>
+        <v>waste</v>
+      </c>
+      <c r="K6" t="str" cm="1">
+        <f t="array" aca="1" ref="K6" ca="1">INDIRECT("'"&amp;K$1&amp;"'!" &amp; ADDRESS($C6+1,4))</f>
+        <v>waste</v>
+      </c>
+      <c r="L6" t="str" cm="1">
+        <f t="array" aca="1" ref="L6" ca="1">INDIRECT("'"&amp;L$1&amp;"'!" &amp; ADDRESS($C6+1,3))</f>
+        <v>road</v>
+      </c>
+      <c r="M6" t="str" cm="1">
+        <f t="array" aca="1" ref="M6" ca="1">INDIRECT("'"&amp;M$1&amp;"'!" &amp; ADDRESS($C6+1,4))</f>
+        <v>water</v>
+      </c>
+      <c r="N6" t="str" cm="1">
+        <f t="array" aca="1" ref="N6" ca="1">INDIRECT("'"&amp;N$1&amp;"'!" &amp; ADDRESS($C6+1,3))</f>
+        <v>waste</v>
+      </c>
+      <c r="O6" t="str" cm="1">
+        <f t="array" aca="1" ref="O6" ca="1">INDIRECT("'"&amp;O$1&amp;"'!" &amp; ADDRESS($C6+1,4))</f>
+        <v>waste</v>
+      </c>
+      <c r="P6" t="str" cm="1">
+        <f t="array" aca="1" ref="P6" ca="1">INDIRECT("'"&amp;P$1&amp;"'!" &amp; ADDRESS($C6+1,3))</f>
+        <v>water</v>
+      </c>
+      <c r="Q6" t="str" cm="1">
+        <f t="array" aca="1" ref="Q6" ca="1">INDIRECT("'"&amp;Q$1&amp;"'!" &amp; ADDRESS($C6+1,4))</f>
+        <v>water</v>
+      </c>
+      <c r="R6" t="str" cm="1">
+        <f t="array" aca="1" ref="R6" ca="1">INDIRECT("'"&amp;R$1&amp;"'!" &amp; ADDRESS($C6+1,3))</f>
+        <v>safety</v>
+      </c>
+      <c r="S6" t="str" cm="1">
+        <f t="array" aca="1" ref="S6" ca="1">INDIRECT("'"&amp;S$1&amp;"'!" &amp; ADDRESS($C6+1,4))</f>
+        <v>safety</v>
+      </c>
+      <c r="T6" t="str" cm="1">
+        <f t="array" aca="1" ref="T6" ca="1">INDIRECT("'"&amp;T$1&amp;"'!" &amp; ADDRESS($C6+1,3))</f>
+        <v>water</v>
+      </c>
+      <c r="U6" t="str" cm="1">
+        <f t="array" aca="1" ref="U6" ca="1">INDIRECT("'"&amp;U$1&amp;"'!" &amp; ADDRESS($C6+1,4))</f>
+        <v>water</v>
+      </c>
+      <c r="V6" t="str" cm="1">
+        <f t="array" aca="1" ref="V6" ca="1">INDIRECT("'"&amp;V$1&amp;"'!" &amp; ADDRESS($C6+1,3))</f>
+        <v>safety</v>
+      </c>
+      <c r="W6" t="str" cm="1">
+        <f t="array" aca="1" ref="W6" ca="1">INDIRECT("'"&amp;W$1&amp;"'!" &amp; ADDRESS($C6+1,4))</f>
+        <v>road</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <f>rand_4!$F$2</f>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="C7">
+        <v>6</v>
+      </c>
+      <c r="D7" t="str" cm="1">
+        <f t="array" aca="1" ref="D7" ca="1">INDIRECT("'"&amp;D$1&amp;"'!" &amp; ADDRESS($C7+1,3))</f>
+        <v>water</v>
+      </c>
+      <c r="E7" t="str" cm="1">
+        <f t="array" aca="1" ref="E7" ca="1">INDIRECT("'"&amp;E$1&amp;"'!" &amp; ADDRESS($C7+1,4))</f>
+        <v>water</v>
+      </c>
+      <c r="F7" t="str" cm="1">
+        <f t="array" aca="1" ref="F7" ca="1">INDIRECT("'"&amp;F$1&amp;"'!" &amp; ADDRESS($C7+1,3))</f>
+        <v>safety</v>
+      </c>
+      <c r="G7" t="str" cm="1">
+        <f t="array" aca="1" ref="G7" ca="1">INDIRECT("'"&amp;G$1&amp;"'!" &amp; ADDRESS($C7+1,4))</f>
+        <v>safety</v>
+      </c>
+      <c r="H7" t="str" cm="1">
+        <f t="array" aca="1" ref="H7" ca="1">INDIRECT("'"&amp;H$1&amp;"'!" &amp; ADDRESS($C7+1,3))</f>
+        <v>road</v>
+      </c>
+      <c r="I7" t="str" cm="1">
+        <f t="array" aca="1" ref="I7" ca="1">INDIRECT("'"&amp;I$1&amp;"'!" &amp; ADDRESS($C7+1,4))</f>
+        <v>road</v>
+      </c>
+      <c r="J7" t="str" cm="1">
+        <f t="array" aca="1" ref="J7" ca="1">INDIRECT("'"&amp;J$1&amp;"'!" &amp; ADDRESS($C7+1,3))</f>
+        <v>safety</v>
+      </c>
+      <c r="K7" t="str" cm="1">
+        <f t="array" aca="1" ref="K7" ca="1">INDIRECT("'"&amp;K$1&amp;"'!" &amp; ADDRESS($C7+1,4))</f>
+        <v>safety</v>
+      </c>
+      <c r="L7" t="str" cm="1">
+        <f t="array" aca="1" ref="L7" ca="1">INDIRECT("'"&amp;L$1&amp;"'!" &amp; ADDRESS($C7+1,3))</f>
+        <v>road</v>
+      </c>
+      <c r="M7" t="str" cm="1">
+        <f t="array" aca="1" ref="M7" ca="1">INDIRECT("'"&amp;M$1&amp;"'!" &amp; ADDRESS($C7+1,4))</f>
+        <v>waste</v>
+      </c>
+      <c r="N7" t="str" cm="1">
+        <f t="array" aca="1" ref="N7" ca="1">INDIRECT("'"&amp;N$1&amp;"'!" &amp; ADDRESS($C7+1,3))</f>
+        <v>safety</v>
+      </c>
+      <c r="O7" t="str" cm="1">
+        <f t="array" aca="1" ref="O7" ca="1">INDIRECT("'"&amp;O$1&amp;"'!" &amp; ADDRESS($C7+1,4))</f>
+        <v>waste</v>
+      </c>
+      <c r="P7" t="str" cm="1">
+        <f t="array" aca="1" ref="P7" ca="1">INDIRECT("'"&amp;P$1&amp;"'!" &amp; ADDRESS($C7+1,3))</f>
+        <v>safety</v>
+      </c>
+      <c r="Q7" t="str" cm="1">
+        <f t="array" aca="1" ref="Q7" ca="1">INDIRECT("'"&amp;Q$1&amp;"'!" &amp; ADDRESS($C7+1,4))</f>
+        <v>safety</v>
+      </c>
+      <c r="R7" t="str" cm="1">
+        <f t="array" aca="1" ref="R7" ca="1">INDIRECT("'"&amp;R$1&amp;"'!" &amp; ADDRESS($C7+1,3))</f>
+        <v>water</v>
+      </c>
+      <c r="S7" t="str" cm="1">
+        <f t="array" aca="1" ref="S7" ca="1">INDIRECT("'"&amp;S$1&amp;"'!" &amp; ADDRESS($C7+1,4))</f>
+        <v>water</v>
+      </c>
+      <c r="T7" t="str" cm="1">
+        <f t="array" aca="1" ref="T7" ca="1">INDIRECT("'"&amp;T$1&amp;"'!" &amp; ADDRESS($C7+1,3))</f>
+        <v>safety</v>
+      </c>
+      <c r="U7" t="str" cm="1">
+        <f t="array" aca="1" ref="U7" ca="1">INDIRECT("'"&amp;U$1&amp;"'!" &amp; ADDRESS($C7+1,4))</f>
+        <v>road</v>
+      </c>
+      <c r="V7" t="str" cm="1">
+        <f t="array" aca="1" ref="V7" ca="1">INDIRECT("'"&amp;V$1&amp;"'!" &amp; ADDRESS($C7+1,3))</f>
+        <v>road</v>
+      </c>
+      <c r="W7" t="str" cm="1">
+        <f t="array" aca="1" ref="W7" ca="1">INDIRECT("'"&amp;W$1&amp;"'!" &amp; ADDRESS($C7+1,4))</f>
+        <v>safety</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <f>rand_5!$F$2</f>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="C8">
+        <v>7</v>
+      </c>
+      <c r="D8" t="str" cm="1">
+        <f t="array" aca="1" ref="D8" ca="1">INDIRECT("'"&amp;D$1&amp;"'!" &amp; ADDRESS($C8+1,3))</f>
+        <v>water</v>
+      </c>
+      <c r="E8" t="str" cm="1">
+        <f t="array" aca="1" ref="E8" ca="1">INDIRECT("'"&amp;E$1&amp;"'!" &amp; ADDRESS($C8+1,4))</f>
+        <v>water</v>
+      </c>
+      <c r="F8" t="str" cm="1">
+        <f t="array" aca="1" ref="F8" ca="1">INDIRECT("'"&amp;F$1&amp;"'!" &amp; ADDRESS($C8+1,3))</f>
+        <v>water</v>
+      </c>
+      <c r="G8" t="str" cm="1">
+        <f t="array" aca="1" ref="G8" ca="1">INDIRECT("'"&amp;G$1&amp;"'!" &amp; ADDRESS($C8+1,4))</f>
+        <v>waste</v>
+      </c>
+      <c r="H8" t="str" cm="1">
+        <f t="array" aca="1" ref="H8" ca="1">INDIRECT("'"&amp;H$1&amp;"'!" &amp; ADDRESS($C8+1,3))</f>
+        <v>waste</v>
+      </c>
+      <c r="I8" t="str" cm="1">
+        <f t="array" aca="1" ref="I8" ca="1">INDIRECT("'"&amp;I$1&amp;"'!" &amp; ADDRESS($C8+1,4))</f>
+        <v>safety</v>
+      </c>
+      <c r="J8" t="str" cm="1">
+        <f t="array" aca="1" ref="J8" ca="1">INDIRECT("'"&amp;J$1&amp;"'!" &amp; ADDRESS($C8+1,3))</f>
+        <v>water</v>
+      </c>
+      <c r="K8" t="str" cm="1">
+        <f t="array" aca="1" ref="K8" ca="1">INDIRECT("'"&amp;K$1&amp;"'!" &amp; ADDRESS($C8+1,4))</f>
+        <v>water</v>
+      </c>
+      <c r="L8" t="str" cm="1">
+        <f t="array" aca="1" ref="L8" ca="1">INDIRECT("'"&amp;L$1&amp;"'!" &amp; ADDRESS($C8+1,3))</f>
+        <v>safety</v>
+      </c>
+      <c r="M8" t="str" cm="1">
+        <f t="array" aca="1" ref="M8" ca="1">INDIRECT("'"&amp;M$1&amp;"'!" &amp; ADDRESS($C8+1,4))</f>
+        <v>safety</v>
+      </c>
+      <c r="N8" t="str" cm="1">
+        <f t="array" aca="1" ref="N8" ca="1">INDIRECT("'"&amp;N$1&amp;"'!" &amp; ADDRESS($C8+1,3))</f>
+        <v>waste</v>
+      </c>
+      <c r="O8" t="str" cm="1">
+        <f t="array" aca="1" ref="O8" ca="1">INDIRECT("'"&amp;O$1&amp;"'!" &amp; ADDRESS($C8+1,4))</f>
+        <v>waste</v>
+      </c>
+      <c r="P8" t="str" cm="1">
+        <f t="array" aca="1" ref="P8" ca="1">INDIRECT("'"&amp;P$1&amp;"'!" &amp; ADDRESS($C8+1,3))</f>
+        <v>waste</v>
+      </c>
+      <c r="Q8" t="str" cm="1">
+        <f t="array" aca="1" ref="Q8" ca="1">INDIRECT("'"&amp;Q$1&amp;"'!" &amp; ADDRESS($C8+1,4))</f>
+        <v>waste</v>
+      </c>
+      <c r="R8" t="str" cm="1">
+        <f t="array" aca="1" ref="R8" ca="1">INDIRECT("'"&amp;R$1&amp;"'!" &amp; ADDRESS($C8+1,3))</f>
+        <v>safety</v>
+      </c>
+      <c r="S8" t="str" cm="1">
+        <f t="array" aca="1" ref="S8" ca="1">INDIRECT("'"&amp;S$1&amp;"'!" &amp; ADDRESS($C8+1,4))</f>
+        <v>safety</v>
+      </c>
+      <c r="T8" t="str" cm="1">
+        <f t="array" aca="1" ref="T8" ca="1">INDIRECT("'"&amp;T$1&amp;"'!" &amp; ADDRESS($C8+1,3))</f>
+        <v>road</v>
+      </c>
+      <c r="U8" t="str" cm="1">
+        <f t="array" aca="1" ref="U8" ca="1">INDIRECT("'"&amp;U$1&amp;"'!" &amp; ADDRESS($C8+1,4))</f>
+        <v>road</v>
+      </c>
+      <c r="V8" t="str" cm="1">
+        <f t="array" aca="1" ref="V8" ca="1">INDIRECT("'"&amp;V$1&amp;"'!" &amp; ADDRESS($C8+1,3))</f>
+        <v>water</v>
+      </c>
+      <c r="W8" t="str" cm="1">
+        <f t="array" aca="1" ref="W8" ca="1">INDIRECT("'"&amp;W$1&amp;"'!" &amp; ADDRESS($C8+1,4))</f>
+        <v>water</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <f>rand_6!$F$2</f>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C9">
+        <v>8</v>
+      </c>
+      <c r="D9" t="str" cm="1">
+        <f t="array" aca="1" ref="D9" ca="1">INDIRECT("'"&amp;D$1&amp;"'!" &amp; ADDRESS($C9+1,3))</f>
+        <v>waste</v>
+      </c>
+      <c r="E9" t="str" cm="1">
+        <f t="array" aca="1" ref="E9" ca="1">INDIRECT("'"&amp;E$1&amp;"'!" &amp; ADDRESS($C9+1,4))</f>
+        <v>safety</v>
+      </c>
+      <c r="F9" t="str" cm="1">
+        <f t="array" aca="1" ref="F9" ca="1">INDIRECT("'"&amp;F$1&amp;"'!" &amp; ADDRESS($C9+1,3))</f>
+        <v>road</v>
+      </c>
+      <c r="G9" t="str" cm="1">
+        <f t="array" aca="1" ref="G9" ca="1">INDIRECT("'"&amp;G$1&amp;"'!" &amp; ADDRESS($C9+1,4))</f>
+        <v>waste</v>
+      </c>
+      <c r="H9" t="str" cm="1">
+        <f t="array" aca="1" ref="H9" ca="1">INDIRECT("'"&amp;H$1&amp;"'!" &amp; ADDRESS($C9+1,3))</f>
+        <v>waste</v>
+      </c>
+      <c r="I9" t="str" cm="1">
+        <f t="array" aca="1" ref="I9" ca="1">INDIRECT("'"&amp;I$1&amp;"'!" &amp; ADDRESS($C9+1,4))</f>
+        <v>road</v>
+      </c>
+      <c r="J9" t="str" cm="1">
+        <f t="array" aca="1" ref="J9" ca="1">INDIRECT("'"&amp;J$1&amp;"'!" &amp; ADDRESS($C9+1,3))</f>
+        <v>safety</v>
+      </c>
+      <c r="K9" t="str" cm="1">
+        <f t="array" aca="1" ref="K9" ca="1">INDIRECT("'"&amp;K$1&amp;"'!" &amp; ADDRESS($C9+1,4))</f>
+        <v>safety</v>
+      </c>
+      <c r="L9" t="str" cm="1">
+        <f t="array" aca="1" ref="L9" ca="1">INDIRECT("'"&amp;L$1&amp;"'!" &amp; ADDRESS($C9+1,3))</f>
+        <v>waste</v>
+      </c>
+      <c r="M9" t="str" cm="1">
+        <f t="array" aca="1" ref="M9" ca="1">INDIRECT("'"&amp;M$1&amp;"'!" &amp; ADDRESS($C9+1,4))</f>
+        <v>waste</v>
+      </c>
+      <c r="N9" t="str" cm="1">
+        <f t="array" aca="1" ref="N9" ca="1">INDIRECT("'"&amp;N$1&amp;"'!" &amp; ADDRESS($C9+1,3))</f>
+        <v>safety</v>
+      </c>
+      <c r="O9" t="str" cm="1">
+        <f t="array" aca="1" ref="O9" ca="1">INDIRECT("'"&amp;O$1&amp;"'!" &amp; ADDRESS($C9+1,4))</f>
+        <v>safety</v>
+      </c>
+      <c r="P9" t="str" cm="1">
+        <f t="array" aca="1" ref="P9" ca="1">INDIRECT("'"&amp;P$1&amp;"'!" &amp; ADDRESS($C9+1,3))</f>
+        <v>safety</v>
+      </c>
+      <c r="Q9" t="str" cm="1">
+        <f t="array" aca="1" ref="Q9" ca="1">INDIRECT("'"&amp;Q$1&amp;"'!" &amp; ADDRESS($C9+1,4))</f>
+        <v>road</v>
+      </c>
+      <c r="R9" t="str" cm="1">
+        <f t="array" aca="1" ref="R9" ca="1">INDIRECT("'"&amp;R$1&amp;"'!" &amp; ADDRESS($C9+1,3))</f>
+        <v>water</v>
+      </c>
+      <c r="S9" t="str" cm="1">
+        <f t="array" aca="1" ref="S9" ca="1">INDIRECT("'"&amp;S$1&amp;"'!" &amp; ADDRESS($C9+1,4))</f>
+        <v>water</v>
+      </c>
+      <c r="T9" t="str" cm="1">
+        <f t="array" aca="1" ref="T9" ca="1">INDIRECT("'"&amp;T$1&amp;"'!" &amp; ADDRESS($C9+1,3))</f>
+        <v>safety</v>
+      </c>
+      <c r="U9" t="str" cm="1">
+        <f t="array" aca="1" ref="U9" ca="1">INDIRECT("'"&amp;U$1&amp;"'!" &amp; ADDRESS($C9+1,4))</f>
+        <v>safety</v>
+      </c>
+      <c r="V9" t="str" cm="1">
+        <f t="array" aca="1" ref="V9" ca="1">INDIRECT("'"&amp;V$1&amp;"'!" &amp; ADDRESS($C9+1,3))</f>
+        <v>road</v>
+      </c>
+      <c r="W9" t="str" cm="1">
+        <f t="array" aca="1" ref="W9" ca="1">INDIRECT("'"&amp;W$1&amp;"'!" &amp; ADDRESS($C9+1,4))</f>
+        <v>waste</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <f>rand_7!$F$2</f>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C10">
+        <v>9</v>
+      </c>
+      <c r="D10" t="str" cm="1">
+        <f t="array" aca="1" ref="D10" ca="1">INDIRECT("'"&amp;D$1&amp;"'!" &amp; ADDRESS($C10+1,3))</f>
+        <v>water</v>
+      </c>
+      <c r="E10" t="str" cm="1">
+        <f t="array" aca="1" ref="E10" ca="1">INDIRECT("'"&amp;E$1&amp;"'!" &amp; ADDRESS($C10+1,4))</f>
+        <v>water</v>
+      </c>
+      <c r="F10" t="str" cm="1">
+        <f t="array" aca="1" ref="F10" ca="1">INDIRECT("'"&amp;F$1&amp;"'!" &amp; ADDRESS($C10+1,3))</f>
+        <v>water</v>
+      </c>
+      <c r="G10" t="str" cm="1">
+        <f t="array" aca="1" ref="G10" ca="1">INDIRECT("'"&amp;G$1&amp;"'!" &amp; ADDRESS($C10+1,4))</f>
+        <v>water</v>
+      </c>
+      <c r="H10" t="str" cm="1">
+        <f t="array" aca="1" ref="H10" ca="1">INDIRECT("'"&amp;H$1&amp;"'!" &amp; ADDRESS($C10+1,3))</f>
+        <v>safety</v>
+      </c>
+      <c r="I10" t="str" cm="1">
+        <f t="array" aca="1" ref="I10" ca="1">INDIRECT("'"&amp;I$1&amp;"'!" &amp; ADDRESS($C10+1,4))</f>
+        <v>water</v>
+      </c>
+      <c r="J10" t="str" cm="1">
+        <f t="array" aca="1" ref="J10" ca="1">INDIRECT("'"&amp;J$1&amp;"'!" &amp; ADDRESS($C10+1,3))</f>
+        <v>waste</v>
+      </c>
+      <c r="K10" t="str" cm="1">
+        <f t="array" aca="1" ref="K10" ca="1">INDIRECT("'"&amp;K$1&amp;"'!" &amp; ADDRESS($C10+1,4))</f>
+        <v>safety</v>
+      </c>
+      <c r="L10" t="str" cm="1">
+        <f t="array" aca="1" ref="L10" ca="1">INDIRECT("'"&amp;L$1&amp;"'!" &amp; ADDRESS($C10+1,3))</f>
+        <v>waste</v>
+      </c>
+      <c r="M10" t="str" cm="1">
+        <f t="array" aca="1" ref="M10" ca="1">INDIRECT("'"&amp;M$1&amp;"'!" &amp; ADDRESS($C10+1,4))</f>
+        <v>road</v>
+      </c>
+      <c r="N10" t="str" cm="1">
+        <f t="array" aca="1" ref="N10" ca="1">INDIRECT("'"&amp;N$1&amp;"'!" &amp; ADDRESS($C10+1,3))</f>
+        <v>road</v>
+      </c>
+      <c r="O10" t="str" cm="1">
+        <f t="array" aca="1" ref="O10" ca="1">INDIRECT("'"&amp;O$1&amp;"'!" &amp; ADDRESS($C10+1,4))</f>
+        <v>road</v>
+      </c>
+      <c r="P10" t="str" cm="1">
+        <f t="array" aca="1" ref="P10" ca="1">INDIRECT("'"&amp;P$1&amp;"'!" &amp; ADDRESS($C10+1,3))</f>
+        <v>road</v>
+      </c>
+      <c r="Q10" t="str" cm="1">
+        <f t="array" aca="1" ref="Q10" ca="1">INDIRECT("'"&amp;Q$1&amp;"'!" &amp; ADDRESS($C10+1,4))</f>
+        <v>road</v>
+      </c>
+      <c r="R10" t="str" cm="1">
+        <f t="array" aca="1" ref="R10" ca="1">INDIRECT("'"&amp;R$1&amp;"'!" &amp; ADDRESS($C10+1,3))</f>
+        <v>waste</v>
+      </c>
+      <c r="S10" t="str" cm="1">
+        <f t="array" aca="1" ref="S10" ca="1">INDIRECT("'"&amp;S$1&amp;"'!" &amp; ADDRESS($C10+1,4))</f>
+        <v>waste</v>
+      </c>
+      <c r="T10" t="str" cm="1">
+        <f t="array" aca="1" ref="T10" ca="1">INDIRECT("'"&amp;T$1&amp;"'!" &amp; ADDRESS($C10+1,3))</f>
+        <v>road</v>
+      </c>
+      <c r="U10" t="str" cm="1">
+        <f t="array" aca="1" ref="U10" ca="1">INDIRECT("'"&amp;U$1&amp;"'!" &amp; ADDRESS($C10+1,4))</f>
+        <v>water</v>
+      </c>
+      <c r="V10" t="str" cm="1">
+        <f t="array" aca="1" ref="V10" ca="1">INDIRECT("'"&amp;V$1&amp;"'!" &amp; ADDRESS($C10+1,3))</f>
+        <v>safety</v>
+      </c>
+      <c r="W10" t="str" cm="1">
+        <f t="array" aca="1" ref="W10" ca="1">INDIRECT("'"&amp;W$1&amp;"'!" &amp; ADDRESS($C10+1,4))</f>
+        <v>waste</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <f>rand_8!$F$2</f>
+        <v>0.5</v>
+      </c>
+      <c r="C11">
+        <v>10</v>
+      </c>
+      <c r="D11" t="str" cm="1">
+        <f t="array" aca="1" ref="D11" ca="1">INDIRECT("'"&amp;D$1&amp;"'!" &amp; ADDRESS($C11+1,3))</f>
+        <v>waste</v>
+      </c>
+      <c r="E11" t="str" cm="1">
+        <f t="array" aca="1" ref="E11" ca="1">INDIRECT("'"&amp;E$1&amp;"'!" &amp; ADDRESS($C11+1,4))</f>
+        <v>waste</v>
+      </c>
+      <c r="F11" t="str" cm="1">
+        <f t="array" aca="1" ref="F11" ca="1">INDIRECT("'"&amp;F$1&amp;"'!" &amp; ADDRESS($C11+1,3))</f>
+        <v>safety</v>
+      </c>
+      <c r="G11" t="str" cm="1">
+        <f t="array" aca="1" ref="G11" ca="1">INDIRECT("'"&amp;G$1&amp;"'!" &amp; ADDRESS($C11+1,4))</f>
+        <v>road</v>
+      </c>
+      <c r="H11" t="str" cm="1">
+        <f t="array" aca="1" ref="H11" ca="1">INDIRECT("'"&amp;H$1&amp;"'!" &amp; ADDRESS($C11+1,3))</f>
+        <v>safety</v>
+      </c>
+      <c r="I11" t="str" cm="1">
+        <f t="array" aca="1" ref="I11" ca="1">INDIRECT("'"&amp;I$1&amp;"'!" &amp; ADDRESS($C11+1,4))</f>
+        <v>safety</v>
+      </c>
+      <c r="J11" t="str" cm="1">
+        <f t="array" aca="1" ref="J11" ca="1">INDIRECT("'"&amp;J$1&amp;"'!" &amp; ADDRESS($C11+1,3))</f>
+        <v>road</v>
+      </c>
+      <c r="K11" t="str" cm="1">
+        <f t="array" aca="1" ref="K11" ca="1">INDIRECT("'"&amp;K$1&amp;"'!" &amp; ADDRESS($C11+1,4))</f>
+        <v>waste</v>
+      </c>
+      <c r="L11" t="str" cm="1">
+        <f t="array" aca="1" ref="L11" ca="1">INDIRECT("'"&amp;L$1&amp;"'!" &amp; ADDRESS($C11+1,3))</f>
+        <v>water</v>
+      </c>
+      <c r="M11" t="str" cm="1">
+        <f t="array" aca="1" ref="M11" ca="1">INDIRECT("'"&amp;M$1&amp;"'!" &amp; ADDRESS($C11+1,4))</f>
+        <v>water</v>
+      </c>
+      <c r="N11" t="str" cm="1">
+        <f t="array" aca="1" ref="N11" ca="1">INDIRECT("'"&amp;N$1&amp;"'!" &amp; ADDRESS($C11+1,3))</f>
+        <v>water</v>
+      </c>
+      <c r="O11" t="str" cm="1">
+        <f t="array" aca="1" ref="O11" ca="1">INDIRECT("'"&amp;O$1&amp;"'!" &amp; ADDRESS($C11+1,4))</f>
+        <v>water</v>
+      </c>
+      <c r="P11" t="str" cm="1">
+        <f t="array" aca="1" ref="P11" ca="1">INDIRECT("'"&amp;P$1&amp;"'!" &amp; ADDRESS($C11+1,3))</f>
+        <v>safety</v>
+      </c>
+      <c r="Q11" t="str" cm="1">
+        <f t="array" aca="1" ref="Q11" ca="1">INDIRECT("'"&amp;Q$1&amp;"'!" &amp; ADDRESS($C11+1,4))</f>
+        <v>safety</v>
+      </c>
+      <c r="R11" t="str" cm="1">
+        <f t="array" aca="1" ref="R11" ca="1">INDIRECT("'"&amp;R$1&amp;"'!" &amp; ADDRESS($C11+1,3))</f>
+        <v>waste</v>
+      </c>
+      <c r="S11" t="str" cm="1">
+        <f t="array" aca="1" ref="S11" ca="1">INDIRECT("'"&amp;S$1&amp;"'!" &amp; ADDRESS($C11+1,4))</f>
+        <v>waste</v>
+      </c>
+      <c r="T11" t="str" cm="1">
+        <f t="array" aca="1" ref="T11" ca="1">INDIRECT("'"&amp;T$1&amp;"'!" &amp; ADDRESS($C11+1,3))</f>
+        <v>water</v>
+      </c>
+      <c r="U11" t="str" cm="1">
+        <f t="array" aca="1" ref="U11" ca="1">INDIRECT("'"&amp;U$1&amp;"'!" &amp; ADDRESS($C11+1,4))</f>
+        <v>road</v>
+      </c>
+      <c r="V11" t="str" cm="1">
+        <f t="array" aca="1" ref="V11" ca="1">INDIRECT("'"&amp;V$1&amp;"'!" &amp; ADDRESS($C11+1,3))</f>
+        <v>road</v>
+      </c>
+      <c r="W11" t="str" cm="1">
+        <f t="array" aca="1" ref="W11" ca="1">INDIRECT("'"&amp;W$1&amp;"'!" &amp; ADDRESS($C11+1,4))</f>
+        <v>safety</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12">
+        <f>rand_9!$F$2</f>
+        <v>0.5</v>
+      </c>
+      <c r="C12">
+        <v>11</v>
+      </c>
+      <c r="D12" t="str" cm="1">
+        <f t="array" aca="1" ref="D12" ca="1">INDIRECT("'"&amp;D$1&amp;"'!" &amp; ADDRESS($C12+1,3))</f>
+        <v>road</v>
+      </c>
+      <c r="E12" t="str" cm="1">
+        <f t="array" aca="1" ref="E12" ca="1">INDIRECT("'"&amp;E$1&amp;"'!" &amp; ADDRESS($C12+1,4))</f>
+        <v>water</v>
+      </c>
+      <c r="F12" t="str" cm="1">
+        <f t="array" aca="1" ref="F12" ca="1">INDIRECT("'"&amp;F$1&amp;"'!" &amp; ADDRESS($C12+1,3))</f>
+        <v>safety</v>
+      </c>
+      <c r="G12" t="str" cm="1">
+        <f t="array" aca="1" ref="G12" ca="1">INDIRECT("'"&amp;G$1&amp;"'!" &amp; ADDRESS($C12+1,4))</f>
+        <v>safety</v>
+      </c>
+      <c r="H12" t="str" cm="1">
+        <f t="array" aca="1" ref="H12" ca="1">INDIRECT("'"&amp;H$1&amp;"'!" &amp; ADDRESS($C12+1,3))</f>
+        <v>waste</v>
+      </c>
+      <c r="I12" t="str" cm="1">
+        <f t="array" aca="1" ref="I12" ca="1">INDIRECT("'"&amp;I$1&amp;"'!" &amp; ADDRESS($C12+1,4))</f>
+        <v>waste</v>
+      </c>
+      <c r="J12" t="str" cm="1">
+        <f t="array" aca="1" ref="J12" ca="1">INDIRECT("'"&amp;J$1&amp;"'!" &amp; ADDRESS($C12+1,3))</f>
+        <v>water</v>
+      </c>
+      <c r="K12" t="str" cm="1">
+        <f t="array" aca="1" ref="K12" ca="1">INDIRECT("'"&amp;K$1&amp;"'!" &amp; ADDRESS($C12+1,4))</f>
+        <v>water</v>
+      </c>
+      <c r="L12" t="str" cm="1">
+        <f t="array" aca="1" ref="L12" ca="1">INDIRECT("'"&amp;L$1&amp;"'!" &amp; ADDRESS($C12+1,3))</f>
+        <v>road</v>
+      </c>
+      <c r="M12" t="str" cm="1">
+        <f t="array" aca="1" ref="M12" ca="1">INDIRECT("'"&amp;M$1&amp;"'!" &amp; ADDRESS($C12+1,4))</f>
+        <v>safety</v>
+      </c>
+      <c r="N12" t="str" cm="1">
+        <f t="array" aca="1" ref="N12" ca="1">INDIRECT("'"&amp;N$1&amp;"'!" &amp; ADDRESS($C12+1,3))</f>
+        <v>waste</v>
+      </c>
+      <c r="O12" t="str" cm="1">
+        <f t="array" aca="1" ref="O12" ca="1">INDIRECT("'"&amp;O$1&amp;"'!" &amp; ADDRESS($C12+1,4))</f>
+        <v>safety</v>
+      </c>
+      <c r="P12" t="str" cm="1">
+        <f t="array" aca="1" ref="P12" ca="1">INDIRECT("'"&amp;P$1&amp;"'!" &amp; ADDRESS($C12+1,3))</f>
+        <v>waste</v>
+      </c>
+      <c r="Q12" t="str" cm="1">
+        <f t="array" aca="1" ref="Q12" ca="1">INDIRECT("'"&amp;Q$1&amp;"'!" &amp; ADDRESS($C12+1,4))</f>
+        <v>safety</v>
+      </c>
+      <c r="R12" t="str" cm="1">
+        <f t="array" aca="1" ref="R12" ca="1">INDIRECT("'"&amp;R$1&amp;"'!" &amp; ADDRESS($C12+1,3))</f>
+        <v>safety</v>
+      </c>
+      <c r="S12" t="str" cm="1">
+        <f t="array" aca="1" ref="S12" ca="1">INDIRECT("'"&amp;S$1&amp;"'!" &amp; ADDRESS($C12+1,4))</f>
+        <v>road</v>
+      </c>
+      <c r="T12" t="str" cm="1">
+        <f t="array" aca="1" ref="T12" ca="1">INDIRECT("'"&amp;T$1&amp;"'!" &amp; ADDRESS($C12+1,3))</f>
+        <v>water</v>
+      </c>
+      <c r="U12" t="str" cm="1">
+        <f t="array" aca="1" ref="U12" ca="1">INDIRECT("'"&amp;U$1&amp;"'!" &amp; ADDRESS($C12+1,4))</f>
+        <v>water</v>
+      </c>
+      <c r="V12" t="str" cm="1">
+        <f t="array" aca="1" ref="V12" ca="1">INDIRECT("'"&amp;V$1&amp;"'!" &amp; ADDRESS($C12+1,3))</f>
+        <v>waste</v>
+      </c>
+      <c r="W12" t="str" cm="1">
+        <f t="array" aca="1" ref="W12" ca="1">INDIRECT("'"&amp;W$1&amp;"'!" &amp; ADDRESS($C12+1,4))</f>
+        <v>waste</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>143</v>
+      </c>
+      <c r="B13">
+        <f>MIN(B3:B12)</f>
+        <v>0.5</v>
+      </c>
+      <c r="C13">
+        <v>12</v>
+      </c>
+      <c r="D13" t="str" cm="1">
+        <f t="array" aca="1" ref="D13" ca="1">INDIRECT("'"&amp;D$1&amp;"'!" &amp; ADDRESS($C13+1,3))</f>
+        <v>road</v>
+      </c>
+      <c r="E13" t="str" cm="1">
+        <f t="array" aca="1" ref="E13" ca="1">INDIRECT("'"&amp;E$1&amp;"'!" &amp; ADDRESS($C13+1,4))</f>
+        <v>safety</v>
+      </c>
+      <c r="F13" t="str" cm="1">
+        <f t="array" aca="1" ref="F13" ca="1">INDIRECT("'"&amp;F$1&amp;"'!" &amp; ADDRESS($C13+1,3))</f>
+        <v>waste</v>
+      </c>
+      <c r="G13" t="str" cm="1">
+        <f t="array" aca="1" ref="G13" ca="1">INDIRECT("'"&amp;G$1&amp;"'!" &amp; ADDRESS($C13+1,4))</f>
+        <v>waste</v>
+      </c>
+      <c r="H13" t="str" cm="1">
+        <f t="array" aca="1" ref="H13" ca="1">INDIRECT("'"&amp;H$1&amp;"'!" &amp; ADDRESS($C13+1,3))</f>
+        <v>water</v>
+      </c>
+      <c r="I13" t="str" cm="1">
+        <f t="array" aca="1" ref="I13" ca="1">INDIRECT("'"&amp;I$1&amp;"'!" &amp; ADDRESS($C13+1,4))</f>
+        <v>water</v>
+      </c>
+      <c r="J13" t="str" cm="1">
+        <f t="array" aca="1" ref="J13" ca="1">INDIRECT("'"&amp;J$1&amp;"'!" &amp; ADDRESS($C13+1,3))</f>
+        <v>road</v>
+      </c>
+      <c r="K13" t="str" cm="1">
+        <f t="array" aca="1" ref="K13" ca="1">INDIRECT("'"&amp;K$1&amp;"'!" &amp; ADDRESS($C13+1,4))</f>
+        <v>road</v>
+      </c>
+      <c r="L13" t="str" cm="1">
+        <f t="array" aca="1" ref="L13" ca="1">INDIRECT("'"&amp;L$1&amp;"'!" &amp; ADDRESS($C13+1,3))</f>
+        <v>water</v>
+      </c>
+      <c r="M13" t="str" cm="1">
+        <f t="array" aca="1" ref="M13" ca="1">INDIRECT("'"&amp;M$1&amp;"'!" &amp; ADDRESS($C13+1,4))</f>
+        <v>water</v>
+      </c>
+      <c r="N13" t="str" cm="1">
+        <f t="array" aca="1" ref="N13" ca="1">INDIRECT("'"&amp;N$1&amp;"'!" &amp; ADDRESS($C13+1,3))</f>
+        <v>road</v>
+      </c>
+      <c r="O13" t="str" cm="1">
+        <f t="array" aca="1" ref="O13" ca="1">INDIRECT("'"&amp;O$1&amp;"'!" &amp; ADDRESS($C13+1,4))</f>
+        <v>safety</v>
+      </c>
+      <c r="P13" t="str" cm="1">
+        <f t="array" aca="1" ref="P13" ca="1">INDIRECT("'"&amp;P$1&amp;"'!" &amp; ADDRESS($C13+1,3))</f>
+        <v>road</v>
+      </c>
+      <c r="Q13" t="str" cm="1">
+        <f t="array" aca="1" ref="Q13" ca="1">INDIRECT("'"&amp;Q$1&amp;"'!" &amp; ADDRESS($C13+1,4))</f>
+        <v>water</v>
+      </c>
+      <c r="R13" t="str" cm="1">
+        <f t="array" aca="1" ref="R13" ca="1">INDIRECT("'"&amp;R$1&amp;"'!" &amp; ADDRESS($C13+1,3))</f>
+        <v>waste</v>
+      </c>
+      <c r="S13" t="str" cm="1">
+        <f t="array" aca="1" ref="S13" ca="1">INDIRECT("'"&amp;S$1&amp;"'!" &amp; ADDRESS($C13+1,4))</f>
+        <v>waste</v>
+      </c>
+      <c r="T13" t="str" cm="1">
+        <f t="array" aca="1" ref="T13" ca="1">INDIRECT("'"&amp;T$1&amp;"'!" &amp; ADDRESS($C13+1,3))</f>
+        <v>road</v>
+      </c>
+      <c r="U13" t="str" cm="1">
+        <f t="array" aca="1" ref="U13" ca="1">INDIRECT("'"&amp;U$1&amp;"'!" &amp; ADDRESS($C13+1,4))</f>
+        <v>road</v>
+      </c>
+      <c r="V13" t="str" cm="1">
+        <f t="array" aca="1" ref="V13" ca="1">INDIRECT("'"&amp;V$1&amp;"'!" &amp; ADDRESS($C13+1,3))</f>
+        <v>waste</v>
+      </c>
+      <c r="W13" t="str" cm="1">
+        <f t="array" aca="1" ref="W13" ca="1">INDIRECT("'"&amp;W$1&amp;"'!" &amp; ADDRESS($C13+1,4))</f>
+        <v>waste</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>144</v>
+      </c>
+      <c r="B14">
+        <f>MAX(B3:B12)</f>
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>145</v>
+      </c>
+      <c r="B15">
+        <f>AVERAGE(B3:B12)</f>
+        <v>0.59166666666666667</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="C16" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16">
+        <f ca="1">COUNTIF(D$2:D$12,$C16)</f>
+        <v>2</v>
+      </c>
+      <c r="E16">
+        <f t="shared" ref="E16:W19" ca="1" si="0">COUNTIF(E$2:E$12,$C16)</f>
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="G16">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H16">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="I16">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="J16">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="K16">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="L16">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="M16">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="N16">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="O16">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="P16">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="Q16">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="R16">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="S16">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="T16">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="U16">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="V16">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="W16">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.3">
+      <c r="C17" t="s">
+        <v>17</v>
+      </c>
+      <c r="D17">
+        <f t="shared" ref="D17:S19" ca="1" si="1">COUNTIF(D$2:D$12,$C17)</f>
+        <v>3</v>
+      </c>
+      <c r="E17">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="F17">
+        <f t="shared" ca="1" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="G17">
+        <f t="shared" ca="1" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="H17">
+        <f t="shared" ca="1" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="I17">
+        <f t="shared" ca="1" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="J17">
+        <f t="shared" ca="1" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="K17">
+        <f t="shared" ca="1" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="L17">
+        <f t="shared" ca="1" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="M17">
+        <f t="shared" ca="1" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="N17">
+        <f t="shared" ca="1" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="O17">
+        <f t="shared" ca="1" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="P17">
+        <f t="shared" ca="1" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="Q17">
+        <f t="shared" ca="1" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="R17">
+        <f t="shared" ca="1" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="S17">
+        <f t="shared" ca="1" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="T17">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="U17">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="V17">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="W17">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.3">
+      <c r="C18" t="s">
+        <v>18</v>
+      </c>
+      <c r="D18">
+        <f t="shared" ca="1" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="E18">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="F18">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="G18">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="H18">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="I18">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="J18">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="K18">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="L18">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="M18">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="N18">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="O18">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="P18">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="Q18">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="R18">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="S18">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="T18">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="U18">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="V18">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="W18">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.3">
+      <c r="C19" t="s">
+        <v>20</v>
+      </c>
+      <c r="D19">
+        <f t="shared" ca="1" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="E19">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="F19">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="G19">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H19">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="I19">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="J19">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="K19">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="L19">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="M19">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="N19">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="O19">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="P19">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="Q19">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="R19">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="S19">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="T19">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="U19">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="V19">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="W19">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="D1:W13">
+    <cfRule type="expression" dxfId="2" priority="2">
+      <formula>MOD(COLUMN(),2)=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E13 G2:G13 I2:I13 K2:K13 M2:M13 O2:O13 Q2:Q13 S2:S13 U2:U13 W2:W13">
+    <cfRule type="expression" dxfId="1" priority="3">
+      <formula>E2&lt;&gt;D2</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E16:E19">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$E$16=$D$16</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F60"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2850,7 +6052,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F67"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3520,7 +6722,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F63"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4154,7 +7356,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:F64"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4796,7 +7998,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:F61"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -5414,7 +8616,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:F64"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -6056,7 +9258,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:F64"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -6696,614 +9898,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:F60"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>134</v>
-      </c>
-      <c r="C2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F2">
-        <v>0.66666666666666663</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>2</v>
-      </c>
-      <c r="B4" t="s">
-        <v>121</v>
-      </c>
-      <c r="C4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>120</v>
-      </c>
-      <c r="C5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>5</v>
-      </c>
-      <c r="B7" t="s">
-        <v>126</v>
-      </c>
-      <c r="C7" t="s">
-        <v>20</v>
-      </c>
-      <c r="D7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>6</v>
-      </c>
-      <c r="B8" t="s">
-        <v>135</v>
-      </c>
-      <c r="C8" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>7</v>
-      </c>
-      <c r="B9" t="s">
-        <v>99</v>
-      </c>
-      <c r="C9" t="s">
-        <v>20</v>
-      </c>
-      <c r="D9" t="s">
-        <v>20</v>
-      </c>
-      <c r="E9" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>8</v>
-      </c>
-      <c r="B10" t="s">
-        <v>5</v>
-      </c>
-      <c r="C10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D10" t="s">
-        <v>17</v>
-      </c>
-      <c r="E10" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>9</v>
-      </c>
-      <c r="B11" t="s">
-        <v>136</v>
-      </c>
-      <c r="C11" t="s">
-        <v>17</v>
-      </c>
-      <c r="D11" t="s">
-        <v>17</v>
-      </c>
-      <c r="E11" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12">
-        <v>10</v>
-      </c>
-      <c r="B12" t="s">
-        <v>137</v>
-      </c>
-      <c r="C12" t="s">
-        <v>18</v>
-      </c>
-      <c r="D12" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13">
-        <v>11</v>
-      </c>
-      <c r="B13" t="s">
-        <v>77</v>
-      </c>
-      <c r="C13" t="s">
-        <v>17</v>
-      </c>
-      <c r="D13" t="s">
-        <v>17</v>
-      </c>
-      <c r="E13" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14">
-        <v>12</v>
-      </c>
-      <c r="E14" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15">
-        <v>13</v>
-      </c>
-      <c r="E15" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16">
-        <v>14</v>
-      </c>
-      <c r="E16" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17">
-        <v>15</v>
-      </c>
-      <c r="E17" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18">
-        <v>16</v>
-      </c>
-      <c r="E18" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19">
-        <v>17</v>
-      </c>
-      <c r="E19" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20">
-        <v>18</v>
-      </c>
-      <c r="E20" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21">
-        <v>19</v>
-      </c>
-      <c r="E21" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22">
-        <v>20</v>
-      </c>
-      <c r="E22" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23">
-        <v>21</v>
-      </c>
-      <c r="E23" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24">
-        <v>22</v>
-      </c>
-      <c r="E24" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25">
-        <v>23</v>
-      </c>
-      <c r="E25" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26">
-        <v>24</v>
-      </c>
-      <c r="E26" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27">
-        <v>25</v>
-      </c>
-      <c r="E27" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28">
-        <v>26</v>
-      </c>
-      <c r="E28" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29">
-        <v>27</v>
-      </c>
-      <c r="E29" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30">
-        <v>28</v>
-      </c>
-      <c r="E30" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31">
-        <v>29</v>
-      </c>
-      <c r="E31" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32">
-        <v>30</v>
-      </c>
-      <c r="E32" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33">
-        <v>31</v>
-      </c>
-      <c r="E33" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A34">
-        <v>32</v>
-      </c>
-      <c r="E34" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35">
-        <v>33</v>
-      </c>
-      <c r="E35" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A36">
-        <v>34</v>
-      </c>
-      <c r="E36" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A37">
-        <v>35</v>
-      </c>
-      <c r="E37" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A38">
-        <v>36</v>
-      </c>
-      <c r="E38" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A39">
-        <v>37</v>
-      </c>
-      <c r="E39" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A40">
-        <v>38</v>
-      </c>
-      <c r="E40" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A41">
-        <v>39</v>
-      </c>
-      <c r="E41" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A42">
-        <v>40</v>
-      </c>
-      <c r="E42" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A43">
-        <v>41</v>
-      </c>
-      <c r="E43" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A44">
-        <v>42</v>
-      </c>
-      <c r="E44" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A45">
-        <v>43</v>
-      </c>
-      <c r="E45" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A46">
-        <v>44</v>
-      </c>
-      <c r="E46" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A47">
-        <v>45</v>
-      </c>
-      <c r="E47" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A48">
-        <v>46</v>
-      </c>
-      <c r="E48" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A49">
-        <v>47</v>
-      </c>
-      <c r="E49" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A50">
-        <v>48</v>
-      </c>
-      <c r="E50" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A51">
-        <v>49</v>
-      </c>
-      <c r="E51" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A52">
-        <v>50</v>
-      </c>
-      <c r="E52" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A53">
-        <v>51</v>
-      </c>
-      <c r="E53" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A54">
-        <v>52</v>
-      </c>
-      <c r="E54" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A55">
-        <v>53</v>
-      </c>
-      <c r="E55" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A56">
-        <v>54</v>
-      </c>
-      <c r="E56" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A57">
-        <v>55</v>
-      </c>
-      <c r="E57" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A58">
-        <v>56</v>
-      </c>
-      <c r="E58" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A59">
-        <v>57</v>
-      </c>
-      <c r="E59" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A60">
-        <v>58</v>
-      </c>
-      <c r="E60" t="s">
-        <v>20</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>